--- a/ResNet18_Results.xlsx
+++ b/ResNet18_Results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
   <si>
     <t>Model</t>
   </si>
@@ -87,7 +87,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.9177777777777778</v>
+        <v>0.92222222222222228</v>
       </c>
     </row>
   </sheetData>

--- a/ResNet18_Results.xlsx
+++ b/ResNet18_Results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6" uniqueCount="3">
   <si>
     <t>Model</t>
   </si>
@@ -87,7 +87,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.92222222222222228</v>
+        <v>0.9177777777777778</v>
       </c>
     </row>
   </sheetData>
